--- a/output/A-S00006179_Renewal_Input_Form.xlsx
+++ b/output/A-S00006179_Renewal_Input_Form.xlsx
@@ -99,12 +99,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -994,31 +994,13 @@
           <t>A-S00006179</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Generally Available</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>ITOM</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>ITOM On Prem</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">per resource unit </t>
-        </is>
-      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="3" t="n"/>
-      <c r="K2" s="4" t="n">
-        <v>15.57</v>
-      </c>
+      <c r="K2" s="4" t="n"/>
       <c r="L2" s="3" t="n"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
@@ -1029,7 +1011,7 @@
       <c r="O2" s="3" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>a</t>
         </is>
       </c>
       <c r="Q2" s="2" t="n">
@@ -1047,9 +1029,7 @@
       <c r="Y2" s="3" t="n"/>
       <c r="Z2" s="3" t="n"/>
       <c r="AA2" s="3" t="n"/>
-      <c r="AB2" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="AB2" s="3" t="n"/>
       <c r="AC2" s="3" t="n"/>
       <c r="AD2" s="3" t="n"/>
       <c r="AE2" s="3" t="n"/>
@@ -1059,56 +1039,44 @@
       <c r="AI2" s="3" t="n"/>
       <c r="AJ2" s="3" t="n"/>
       <c r="AK2" s="3" t="n"/>
-      <c r="AL2" s="6" t="inlineStr">
-        <is>
-          <t>30-JUN-2026</t>
-        </is>
-      </c>
-      <c r="AM2" s="6" t="inlineStr">
-        <is>
-          <t>29-JUN-2027</t>
-        </is>
-      </c>
-      <c r="AN2" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="AL2" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AM2" s="5" t="inlineStr">
+        <is>
+          <t>2027-06-29</t>
+        </is>
+      </c>
+      <c r="AN2" s="6" t="n"/>
       <c r="AO2" s="3" t="n"/>
       <c r="AP2" s="3" t="n"/>
       <c r="AQ2" s="3" t="n"/>
       <c r="AR2" s="3" t="n"/>
-      <c r="AS2" s="8" t="n">
+      <c r="AS2" s="7" t="n">
         <v>0.9946478270177692</v>
       </c>
-      <c r="AT2" s="8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AT2" s="3" t="n"/>
       <c r="AU2" s="3" t="n"/>
       <c r="AV2" s="3" t="n"/>
       <c r="AW2" s="3" t="n"/>
-      <c r="AX2" s="9" t="n">
+      <c r="AX2" s="8" t="n">
         <v>0.04583333333333334</v>
       </c>
-      <c r="AY2" s="9" t="n">
+      <c r="AY2" s="3" t="n"/>
+      <c r="AZ2" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BA2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AZ2" s="10" t="n">
-        <v>1.008333333333333</v>
-      </c>
-      <c r="BA2" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" s="10" t="n">
-        <v>1.008333333333333</v>
-      </c>
-      <c r="BC2" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD2" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE2" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="BB2" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC2" s="10" t="n"/>
+      <c r="BD2" s="10" t="n"/>
+      <c r="BE2" s="6" t="n"/>
       <c r="BF2" s="3" t="n"/>
       <c r="BG2" s="3" t="n"/>
       <c r="BH2" s="3" t="n"/>
@@ -1149,31 +1117,13 @@
           <t>A-S00006179</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Generally Available</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>ITOM</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>ITOM On Prem</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">per third-party software </t>
-        </is>
-      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
-      <c r="K3" s="4" t="n">
-        <v>3786.31</v>
-      </c>
+      <c r="K3" s="4" t="n"/>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -1184,7 +1134,7 @@
       <c r="O3" s="3" t="n"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>a</t>
         </is>
       </c>
       <c r="Q3" s="2" t="n">
@@ -1202,9 +1152,7 @@
       <c r="Y3" s="3" t="n"/>
       <c r="Z3" s="3" t="n"/>
       <c r="AA3" s="3" t="n"/>
-      <c r="AB3" s="5" t="n">
-        <v>35683</v>
-      </c>
+      <c r="AB3" s="3" t="n"/>
       <c r="AC3" s="3" t="n"/>
       <c r="AD3" s="3" t="n"/>
       <c r="AE3" s="3" t="n"/>
@@ -1214,56 +1162,44 @@
       <c r="AI3" s="3" t="n"/>
       <c r="AJ3" s="3" t="n"/>
       <c r="AK3" s="3" t="n"/>
-      <c r="AL3" s="6" t="inlineStr">
-        <is>
-          <t>30-JUN-2026</t>
-        </is>
-      </c>
-      <c r="AM3" s="6" t="inlineStr">
-        <is>
-          <t>29-JUN-2027</t>
-        </is>
-      </c>
-      <c r="AN3" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="AL3" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AM3" s="5" t="inlineStr">
+        <is>
+          <t>2027-06-29</t>
+        </is>
+      </c>
+      <c r="AN3" s="6" t="n"/>
       <c r="AO3" s="3" t="n"/>
       <c r="AP3" s="3" t="n"/>
       <c r="AQ3" s="3" t="n"/>
       <c r="AR3" s="3" t="n"/>
-      <c r="AS3" s="8" t="n">
+      <c r="AS3" s="7" t="n">
         <v>0.7012922872136724</v>
       </c>
-      <c r="AT3" s="8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AT3" s="3" t="n"/>
       <c r="AU3" s="3" t="n"/>
       <c r="AV3" s="3" t="n"/>
       <c r="AW3" s="3" t="n"/>
-      <c r="AX3" s="9" t="n">
+      <c r="AX3" s="8" t="n">
         <v>622.0500000000001</v>
       </c>
-      <c r="AY3" s="9" t="n">
+      <c r="AY3" s="3" t="n"/>
+      <c r="AZ3" s="9" t="n">
+        <v>22393.8</v>
+      </c>
+      <c r="BA3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AZ3" s="10" t="n">
-        <v>20527.65</v>
-      </c>
-      <c r="BA3" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" s="10" t="n">
-        <v>20527.65</v>
-      </c>
-      <c r="BC3" s="5" t="n">
-        <v>40716</v>
-      </c>
-      <c r="BD3" s="5" t="n">
-        <v>39439</v>
-      </c>
-      <c r="BE3" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="BB3" s="9" t="n">
+        <v>22393.8</v>
+      </c>
+      <c r="BC3" s="10" t="n"/>
+      <c r="BD3" s="10" t="n"/>
+      <c r="BE3" s="6" t="n"/>
       <c r="BF3" s="3" t="n"/>
       <c r="BG3" s="3" t="n"/>
       <c r="BH3" s="3" t="n"/>
@@ -1304,31 +1240,13 @@
           <t>A-S00006179</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Withdrawn</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>ITSM</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>ITSM On Prem</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">per concurrent user </t>
-        </is>
-      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
-      <c r="K4" s="4" t="n">
-        <v>791.12</v>
-      </c>
+      <c r="K4" s="4" t="n"/>
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
@@ -1339,7 +1257,7 @@
       <c r="O4" s="3" t="n"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>a</t>
         </is>
       </c>
       <c r="Q4" s="2" t="n">
@@ -1357,9 +1275,7 @@
       <c r="Y4" s="3" t="n"/>
       <c r="Z4" s="3" t="n"/>
       <c r="AA4" s="3" t="n"/>
-      <c r="AB4" s="5" t="n">
-        <v>3872</v>
-      </c>
+      <c r="AB4" s="3" t="n"/>
       <c r="AC4" s="3" t="n"/>
       <c r="AD4" s="3" t="n"/>
       <c r="AE4" s="3" t="n"/>
@@ -1369,56 +1285,44 @@
       <c r="AI4" s="3" t="n"/>
       <c r="AJ4" s="3" t="n"/>
       <c r="AK4" s="3" t="n"/>
-      <c r="AL4" s="6" t="inlineStr">
-        <is>
-          <t>30-JUN-2026</t>
-        </is>
-      </c>
-      <c r="AM4" s="6" t="inlineStr">
-        <is>
-          <t>29-JUN-2027</t>
-        </is>
-      </c>
-      <c r="AN4" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="AL4" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AM4" s="5" t="inlineStr">
+        <is>
+          <t>2027-06-29</t>
+        </is>
+      </c>
+      <c r="AN4" s="6" t="n"/>
       <c r="AO4" s="3" t="n"/>
       <c r="AP4" s="3" t="n"/>
       <c r="AQ4" s="3" t="n"/>
       <c r="AR4" s="3" t="n"/>
-      <c r="AS4" s="8" t="n">
+      <c r="AS4" s="7" t="n">
         <v>0.9941828251929754</v>
       </c>
-      <c r="AT4" s="8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AT4" s="3" t="n"/>
       <c r="AU4" s="3" t="n"/>
       <c r="AV4" s="3" t="n"/>
       <c r="AW4" s="3" t="n"/>
-      <c r="AX4" s="9" t="n">
+      <c r="AX4" s="8" t="n">
         <v>2.531145833333313</v>
       </c>
-      <c r="AY4" s="9" t="n">
+      <c r="AY4" s="3" t="n"/>
+      <c r="AZ4" s="9" t="n">
+        <v>2429.899999999981</v>
+      </c>
+      <c r="BA4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AZ4" s="10" t="n">
-        <v>2227.408333333316</v>
-      </c>
-      <c r="BA4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" s="10" t="n">
-        <v>2227.408333333316</v>
-      </c>
-      <c r="BC4" s="5" t="n">
-        <v>4418</v>
-      </c>
-      <c r="BD4" s="5" t="n">
-        <v>4280</v>
-      </c>
-      <c r="BE4" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="BB4" s="9" t="n">
+        <v>2429.899999999981</v>
+      </c>
+      <c r="BC4" s="10" t="n"/>
+      <c r="BD4" s="10" t="n"/>
+      <c r="BE4" s="6" t="n"/>
       <c r="BF4" s="3" t="n"/>
       <c r="BG4" s="3" t="n"/>
       <c r="BH4" s="3" t="n"/>
@@ -1459,31 +1363,13 @@
           <t>A-S00006179</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Withdrawn</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>ITSM</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>ITSM On Prem</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">per named user </t>
-        </is>
-      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
-      <c r="K5" s="4" t="n">
-        <v>263.71</v>
-      </c>
+      <c r="K5" s="4" t="n"/>
       <c r="L5" s="3" t="n"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
@@ -1494,7 +1380,7 @@
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>a</t>
         </is>
       </c>
       <c r="Q5" s="2" t="n">
@@ -1512,9 +1398,7 @@
       <c r="Y5" s="3" t="n"/>
       <c r="Z5" s="3" t="n"/>
       <c r="AA5" s="3" t="n"/>
-      <c r="AB5" s="5" t="n">
-        <v>807</v>
-      </c>
+      <c r="AB5" s="3" t="n"/>
       <c r="AC5" s="3" t="n"/>
       <c r="AD5" s="3" t="n"/>
       <c r="AE5" s="3" t="n"/>
@@ -1524,56 +1408,44 @@
       <c r="AI5" s="3" t="n"/>
       <c r="AJ5" s="3" t="n"/>
       <c r="AK5" s="3" t="n"/>
-      <c r="AL5" s="6" t="inlineStr">
-        <is>
-          <t>30-JUN-2026</t>
-        </is>
-      </c>
-      <c r="AM5" s="6" t="inlineStr">
-        <is>
-          <t>29-JUN-2027</t>
-        </is>
-      </c>
-      <c r="AN5" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="AL5" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AM5" s="5" t="inlineStr">
+        <is>
+          <t>2027-06-29</t>
+        </is>
+      </c>
+      <c r="AN5" s="6" t="n"/>
       <c r="AO5" s="3" t="n"/>
       <c r="AP5" s="3" t="n"/>
       <c r="AQ5" s="3" t="n"/>
       <c r="AR5" s="3" t="n"/>
-      <c r="AS5" s="8" t="n">
+      <c r="AS5" s="7" t="n">
         <v>0.9941855320870148</v>
       </c>
-      <c r="AT5" s="8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AT5" s="3" t="n"/>
       <c r="AU5" s="3" t="n"/>
       <c r="AV5" s="3" t="n"/>
       <c r="AW5" s="3" t="n"/>
-      <c r="AX5" s="9" t="n">
+      <c r="AX5" s="8" t="n">
         <v>0.8433333333333347</v>
       </c>
-      <c r="AY5" s="9" t="n">
+      <c r="AY5" s="3" t="n"/>
+      <c r="AZ5" s="9" t="n">
+        <v>506.0000000000009</v>
+      </c>
+      <c r="BA5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AZ5" s="10" t="n">
-        <v>463.8333333333341</v>
-      </c>
-      <c r="BA5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" s="10" t="n">
-        <v>463.8333333333341</v>
-      </c>
-      <c r="BC5" s="5" t="n">
-        <v>920</v>
-      </c>
-      <c r="BD5" s="5" t="n">
-        <v>892</v>
-      </c>
-      <c r="BE5" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="BB5" s="9" t="n">
+        <v>506.0000000000009</v>
+      </c>
+      <c r="BC5" s="10" t="n"/>
+      <c r="BD5" s="10" t="n"/>
+      <c r="BE5" s="6" t="n"/>
       <c r="BF5" s="3" t="n"/>
       <c r="BG5" s="3" t="n"/>
       <c r="BH5" s="3" t="n"/>
@@ -1614,31 +1486,13 @@
           <t>A-S00006179</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Generally Available</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Remediate</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Remediate On Prem</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">per managed asset - server endpoint </t>
-        </is>
-      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
-      <c r="K6" s="4" t="n">
-        <v>130.37</v>
-      </c>
+      <c r="K6" s="4" t="n"/>
       <c r="L6" s="3" t="n"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -1649,7 +1503,7 @@
       <c r="O6" s="3" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>a</t>
         </is>
       </c>
       <c r="Q6" s="2" t="n">
@@ -1667,9 +1521,7 @@
       <c r="Y6" s="3" t="n"/>
       <c r="Z6" s="3" t="n"/>
       <c r="AA6" s="3" t="n"/>
-      <c r="AB6" s="5" t="n">
-        <v>159522</v>
-      </c>
+      <c r="AB6" s="3" t="n"/>
       <c r="AC6" s="3" t="n"/>
       <c r="AD6" s="3" t="n"/>
       <c r="AE6" s="3" t="n"/>
@@ -1679,56 +1531,44 @@
       <c r="AI6" s="3" t="n"/>
       <c r="AJ6" s="3" t="n"/>
       <c r="AK6" s="3" t="n"/>
-      <c r="AL6" s="6" t="inlineStr">
-        <is>
-          <t>30-JUN-2026</t>
-        </is>
-      </c>
-      <c r="AM6" s="6" t="inlineStr">
-        <is>
-          <t>29-JUN-2027</t>
-        </is>
-      </c>
-      <c r="AN6" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="AL6" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AM6" s="5" t="inlineStr">
+        <is>
+          <t>2027-06-29</t>
+        </is>
+      </c>
+      <c r="AN6" s="6" t="n"/>
       <c r="AO6" s="3" t="n"/>
       <c r="AP6" s="3" t="n"/>
       <c r="AQ6" s="3" t="n"/>
       <c r="AR6" s="3" t="n"/>
-      <c r="AS6" s="8" t="n">
+      <c r="AS6" s="7" t="n">
         <v>0.9943649804402853</v>
       </c>
-      <c r="AT6" s="8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AT6" s="3" t="n"/>
       <c r="AU6" s="3" t="n"/>
       <c r="AV6" s="3" t="n"/>
       <c r="AW6" s="3" t="n"/>
-      <c r="AX6" s="9" t="n">
+      <c r="AX6" s="8" t="n">
         <v>0.4040506250000018</v>
       </c>
-      <c r="AY6" s="9" t="n">
+      <c r="AY6" s="3" t="n"/>
+      <c r="AZ6" s="9" t="n">
+        <v>96972.15000000043</v>
+      </c>
+      <c r="BA6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AZ6" s="10" t="n">
-        <v>88891.13750000039</v>
-      </c>
-      <c r="BA6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" s="10" t="n">
-        <v>88891.13750000039</v>
-      </c>
-      <c r="BC6" s="5" t="n">
-        <v>176313</v>
-      </c>
-      <c r="BD6" s="5" t="n">
-        <v>176313</v>
-      </c>
-      <c r="BE6" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="BB6" s="9" t="n">
+        <v>96972.15000000043</v>
+      </c>
+      <c r="BC6" s="10" t="n"/>
+      <c r="BD6" s="10" t="n"/>
+      <c r="BE6" s="6" t="n"/>
       <c r="BF6" s="3" t="n"/>
       <c r="BG6" s="3" t="n"/>
       <c r="BH6" s="3" t="n"/>
@@ -1769,31 +1609,13 @@
           <t>A-S00006179</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Generally Available</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Remediate</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Remediate On Prem</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">per enterprise </t>
-        </is>
-      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
-      <c r="K7" s="4" t="n">
-        <v>1869.27</v>
-      </c>
+      <c r="K7" s="4" t="n"/>
       <c r="L7" s="3" t="n"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
@@ -1804,7 +1626,7 @@
       <c r="O7" s="3" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>a</t>
         </is>
       </c>
       <c r="Q7" s="2" t="n">
@@ -1822,9 +1644,7 @@
       <c r="Y7" s="3" t="n"/>
       <c r="Z7" s="3" t="n"/>
       <c r="AA7" s="3" t="n"/>
-      <c r="AB7" s="5" t="n">
-        <v>120</v>
-      </c>
+      <c r="AB7" s="3" t="n"/>
       <c r="AC7" s="3" t="n"/>
       <c r="AD7" s="3" t="n"/>
       <c r="AE7" s="3" t="n"/>
@@ -1834,56 +1654,44 @@
       <c r="AI7" s="3" t="n"/>
       <c r="AJ7" s="3" t="n"/>
       <c r="AK7" s="3" t="n"/>
-      <c r="AL7" s="6" t="inlineStr">
-        <is>
-          <t>30-JUN-2026</t>
-        </is>
-      </c>
-      <c r="AM7" s="6" t="inlineStr">
-        <is>
-          <t>29-JUN-2027</t>
-        </is>
-      </c>
-      <c r="AN7" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="AL7" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AM7" s="5" t="inlineStr">
+        <is>
+          <t>2027-06-29</t>
+        </is>
+      </c>
+      <c r="AN7" s="6" t="n"/>
       <c r="AO7" s="3" t="n"/>
       <c r="AP7" s="3" t="n"/>
       <c r="AQ7" s="3" t="n"/>
       <c r="AR7" s="3" t="n"/>
-      <c r="AS7" s="8" t="n">
+      <c r="AS7" s="7" t="n">
         <v>0.9943828339405222</v>
       </c>
-      <c r="AT7" s="8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AT7" s="3" t="n"/>
       <c r="AU7" s="3" t="n"/>
       <c r="AV7" s="3" t="n"/>
       <c r="AW7" s="3" t="n"/>
-      <c r="AX7" s="9" t="n">
+      <c r="AX7" s="8" t="n">
         <v>5.775000000000056</v>
       </c>
-      <c r="AY7" s="9" t="n">
+      <c r="AY7" s="3" t="n"/>
+      <c r="AZ7" s="9" t="n">
+        <v>69.30000000000068</v>
+      </c>
+      <c r="BA7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AZ7" s="10" t="n">
-        <v>63.52500000000062</v>
-      </c>
-      <c r="BA7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" s="10" t="n">
-        <v>63.52500000000062</v>
-      </c>
-      <c r="BC7" s="5" t="n">
-        <v>126</v>
-      </c>
-      <c r="BD7" s="5" t="n">
-        <v>126</v>
-      </c>
-      <c r="BE7" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="BB7" s="9" t="n">
+        <v>69.30000000000068</v>
+      </c>
+      <c r="BC7" s="10" t="n"/>
+      <c r="BD7" s="10" t="n"/>
+      <c r="BE7" s="6" t="n"/>
       <c r="BF7" s="3" t="n"/>
       <c r="BG7" s="3" t="n"/>
       <c r="BH7" s="3" t="n"/>
@@ -1924,31 +1732,13 @@
           <t>A-S00006179</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Generally Available</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Remediate</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Remediate On Prem</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">per adapter </t>
-        </is>
-      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
-      <c r="K8" s="4" t="n">
-        <v>3738.53</v>
-      </c>
+      <c r="K8" s="4" t="n"/>
       <c r="L8" s="3" t="n"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
@@ -1959,7 +1749,7 @@
       <c r="O8" s="3" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>a</t>
         </is>
       </c>
       <c r="Q8" s="2" t="n">
@@ -1977,9 +1767,7 @@
       <c r="Y8" s="3" t="n"/>
       <c r="Z8" s="3" t="n"/>
       <c r="AA8" s="3" t="n"/>
-      <c r="AB8" s="5" t="n">
-        <v>722</v>
-      </c>
+      <c r="AB8" s="3" t="n"/>
       <c r="AC8" s="3" t="n"/>
       <c r="AD8" s="3" t="n"/>
       <c r="AE8" s="3" t="n"/>
@@ -1989,56 +1777,44 @@
       <c r="AI8" s="3" t="n"/>
       <c r="AJ8" s="3" t="n"/>
       <c r="AK8" s="3" t="n"/>
-      <c r="AL8" s="6" t="inlineStr">
-        <is>
-          <t>30-JUN-2026</t>
-        </is>
-      </c>
-      <c r="AM8" s="6" t="inlineStr">
-        <is>
-          <t>29-JUN-2027</t>
-        </is>
-      </c>
-      <c r="AN8" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="AL8" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AM8" s="5" t="inlineStr">
+        <is>
+          <t>2027-06-29</t>
+        </is>
+      </c>
+      <c r="AN8" s="6" t="n"/>
       <c r="AO8" s="3" t="n"/>
       <c r="AP8" s="3" t="n"/>
       <c r="AQ8" s="3" t="n"/>
       <c r="AR8" s="3" t="n"/>
-      <c r="AS8" s="8" t="n">
+      <c r="AS8" s="7" t="n">
         <v>0.9943679586480366</v>
       </c>
-      <c r="AT8" s="8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AT8" s="3" t="n"/>
       <c r="AU8" s="3" t="n"/>
       <c r="AV8" s="3" t="n"/>
       <c r="AW8" s="3" t="n"/>
-      <c r="AX8" s="9" t="n">
+      <c r="AX8" s="8" t="n">
         <v>11.58055555555561</v>
       </c>
-      <c r="AY8" s="9" t="n">
+      <c r="AY8" s="3" t="n"/>
+      <c r="AZ8" s="9" t="n">
+        <v>416.900000000002</v>
+      </c>
+      <c r="BA8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AZ8" s="10" t="n">
-        <v>382.1583333333351</v>
-      </c>
-      <c r="BA8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" s="10" t="n">
-        <v>382.1583333333351</v>
-      </c>
-      <c r="BC8" s="5" t="n">
-        <v>758</v>
-      </c>
-      <c r="BD8" s="5" t="n">
-        <v>758</v>
-      </c>
-      <c r="BE8" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="BB8" s="9" t="n">
+        <v>416.900000000002</v>
+      </c>
+      <c r="BC8" s="10" t="n"/>
+      <c r="BD8" s="10" t="n"/>
+      <c r="BE8" s="6" t="n"/>
       <c r="BF8" s="3" t="n"/>
       <c r="BG8" s="3" t="n"/>
       <c r="BH8" s="3" t="n"/>
@@ -2069,7 +1845,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TrueSight Orchestration - Development Pack License Add- on</t>
+          <t>TrueSight Orchestration - Development Pack License Add-on</t>
         </is>
       </c>
       <c r="B9" s="3" t="n"/>
@@ -2079,31 +1855,13 @@
           <t>A-S00006179</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Generally Available</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Remediate</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Remediate On Prem</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">per enterprise </t>
-        </is>
-      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
-      <c r="K9" s="4" t="n">
-        <v>24300.54</v>
-      </c>
+      <c r="K9" s="4" t="n"/>
       <c r="L9" s="3" t="n"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
@@ -2114,7 +1872,7 @@
       <c r="O9" s="3" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>a</t>
         </is>
       </c>
       <c r="Q9" s="2" t="n">
@@ -2132,9 +1890,7 @@
       <c r="Y9" s="3" t="n"/>
       <c r="Z9" s="3" t="n"/>
       <c r="AA9" s="3" t="n"/>
-      <c r="AB9" s="5" t="n">
-        <v>1565</v>
-      </c>
+      <c r="AB9" s="3" t="n"/>
       <c r="AC9" s="3" t="n"/>
       <c r="AD9" s="3" t="n"/>
       <c r="AE9" s="3" t="n"/>
@@ -2144,56 +1900,44 @@
       <c r="AI9" s="3" t="n"/>
       <c r="AJ9" s="3" t="n"/>
       <c r="AK9" s="3" t="n"/>
-      <c r="AL9" s="6" t="inlineStr">
-        <is>
-          <t>30-JUN-2026</t>
-        </is>
-      </c>
-      <c r="AM9" s="6" t="inlineStr">
-        <is>
-          <t>29-JUN-2027</t>
-        </is>
-      </c>
-      <c r="AN9" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="AL9" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AM9" s="5" t="inlineStr">
+        <is>
+          <t>2027-06-29</t>
+        </is>
+      </c>
+      <c r="AN9" s="6" t="n"/>
       <c r="AO9" s="3" t="n"/>
       <c r="AP9" s="3" t="n"/>
       <c r="AQ9" s="3" t="n"/>
       <c r="AR9" s="3" t="n"/>
-      <c r="AS9" s="8" t="n">
+      <c r="AS9" s="7" t="n">
         <v>0.994365694479766</v>
       </c>
-      <c r="AT9" s="8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AT9" s="3" t="n"/>
       <c r="AU9" s="3" t="n"/>
       <c r="AV9" s="3" t="n"/>
       <c r="AW9" s="3" t="n"/>
-      <c r="AX9" s="9" t="n">
+      <c r="AX9" s="8" t="n">
         <v>75.30416666666731</v>
       </c>
-      <c r="AY9" s="9" t="n">
+      <c r="AY9" s="3" t="n"/>
+      <c r="AZ9" s="9" t="n">
+        <v>903.6500000000078</v>
+      </c>
+      <c r="BA9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AZ9" s="10" t="n">
-        <v>828.3458333333405</v>
-      </c>
-      <c r="BA9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" s="10" t="n">
-        <v>828.3458333333405</v>
-      </c>
-      <c r="BC9" s="5" t="n">
-        <v>1643</v>
-      </c>
-      <c r="BD9" s="5" t="n">
-        <v>1643</v>
-      </c>
-      <c r="BE9" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="BB9" s="9" t="n">
+        <v>903.6500000000078</v>
+      </c>
+      <c r="BC9" s="10" t="n"/>
+      <c r="BD9" s="10" t="n"/>
+      <c r="BE9" s="6" t="n"/>
       <c r="BF9" s="3" t="n"/>
       <c r="BG9" s="3" t="n"/>
       <c r="BH9" s="3" t="n"/>
@@ -2234,31 +1978,13 @@
           <t>A-S00006179</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Generally Available</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Remediate</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Remediate On Prem</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">per instance </t>
-        </is>
-      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
-      <c r="K10" s="4" t="n">
-        <v>8224.799999999999</v>
-      </c>
+      <c r="K10" s="4" t="n"/>
       <c r="L10" s="3" t="n"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
@@ -2269,7 +1995,7 @@
       <c r="O10" s="3" t="n"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>a</t>
         </is>
       </c>
       <c r="Q10" s="2" t="n">
@@ -2287,9 +2013,7 @@
       <c r="Y10" s="3" t="n"/>
       <c r="Z10" s="3" t="n"/>
       <c r="AA10" s="3" t="n"/>
-      <c r="AB10" s="5" t="n">
-        <v>2119</v>
-      </c>
+      <c r="AB10" s="3" t="n"/>
       <c r="AC10" s="3" t="n"/>
       <c r="AD10" s="3" t="n"/>
       <c r="AE10" s="3" t="n"/>
@@ -2299,56 +2023,44 @@
       <c r="AI10" s="3" t="n"/>
       <c r="AJ10" s="3" t="n"/>
       <c r="AK10" s="3" t="n"/>
-      <c r="AL10" s="6" t="inlineStr">
-        <is>
-          <t>30-JUN-2026</t>
-        </is>
-      </c>
-      <c r="AM10" s="6" t="inlineStr">
-        <is>
-          <t>29-JUN-2027</t>
-        </is>
-      </c>
-      <c r="AN10" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="AL10" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AM10" s="5" t="inlineStr">
+        <is>
+          <t>2027-06-29</t>
+        </is>
+      </c>
+      <c r="AN10" s="6" t="n"/>
       <c r="AO10" s="3" t="n"/>
       <c r="AP10" s="3" t="n"/>
       <c r="AQ10" s="3" t="n"/>
       <c r="AR10" s="3" t="n"/>
-      <c r="AS10" s="8" t="n">
+      <c r="AS10" s="7" t="n">
         <v>0.994364098012515</v>
       </c>
-      <c r="AT10" s="8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AT10" s="3" t="n"/>
       <c r="AU10" s="3" t="n"/>
       <c r="AV10" s="3" t="n"/>
       <c r="AW10" s="3" t="n"/>
-      <c r="AX10" s="9" t="n">
+      <c r="AX10" s="8" t="n">
         <v>25.49479166666656</v>
       </c>
-      <c r="AY10" s="9" t="n">
+      <c r="AY10" s="3" t="n"/>
+      <c r="AZ10" s="9" t="n">
+        <v>1223.749999999995</v>
+      </c>
+      <c r="BA10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AZ10" s="10" t="n">
-        <v>1121.770833333329</v>
-      </c>
-      <c r="BA10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" s="10" t="n">
-        <v>1121.770833333329</v>
-      </c>
-      <c r="BC10" s="5" t="n">
-        <v>2225</v>
-      </c>
-      <c r="BD10" s="5" t="n">
-        <v>2225</v>
-      </c>
-      <c r="BE10" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="BB10" s="9" t="n">
+        <v>1223.749999999995</v>
+      </c>
+      <c r="BC10" s="10" t="n"/>
+      <c r="BD10" s="10" t="n"/>
+      <c r="BE10" s="6" t="n"/>
       <c r="BF10" s="3" t="n"/>
       <c r="BG10" s="3" t="n"/>
       <c r="BH10" s="3" t="n"/>
@@ -2389,31 +2101,13 @@
           <t>A-S00006179</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Generally Available</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Remediate</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Remediate On Prem</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">per enterprise </t>
-        </is>
-      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="n"/>
-      <c r="K11" s="4" t="n">
-        <v>2317.55</v>
-      </c>
+      <c r="K11" s="4" t="n"/>
       <c r="L11" s="3" t="n"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -2424,7 +2118,7 @@
       <c r="O11" s="3" t="n"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>a</t>
         </is>
       </c>
       <c r="Q11" s="2" t="n">
@@ -2442,9 +2136,7 @@
       <c r="Y11" s="3" t="n"/>
       <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="n"/>
-      <c r="AB11" s="5" t="n">
-        <v>149</v>
-      </c>
+      <c r="AB11" s="3" t="n"/>
       <c r="AC11" s="3" t="n"/>
       <c r="AD11" s="3" t="n"/>
       <c r="AE11" s="3" t="n"/>
@@ -2454,56 +2146,44 @@
       <c r="AI11" s="3" t="n"/>
       <c r="AJ11" s="3" t="n"/>
       <c r="AK11" s="3" t="n"/>
-      <c r="AL11" s="6" t="inlineStr">
-        <is>
-          <t>30-JUN-2026</t>
-        </is>
-      </c>
-      <c r="AM11" s="6" t="inlineStr">
-        <is>
-          <t>29-JUN-2027</t>
-        </is>
-      </c>
-      <c r="AN11" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="AL11" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AM11" s="5" t="inlineStr">
+        <is>
+          <t>2027-06-29</t>
+        </is>
+      </c>
+      <c r="AN11" s="6" t="n"/>
       <c r="AO11" s="3" t="n"/>
       <c r="AP11" s="3" t="n"/>
       <c r="AQ11" s="3" t="n"/>
       <c r="AR11" s="3" t="n"/>
-      <c r="AS11" s="8" t="n">
+      <c r="AS11" s="7" t="n">
         <v>0.994354670521312</v>
       </c>
-      <c r="AT11" s="8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AT11" s="3" t="n"/>
       <c r="AU11" s="3" t="n"/>
       <c r="AV11" s="3" t="n"/>
       <c r="AW11" s="3" t="n"/>
-      <c r="AX11" s="9" t="n">
+      <c r="AX11" s="8" t="n">
         <v>7.19583333333337</v>
       </c>
-      <c r="AY11" s="9" t="n">
+      <c r="AY11" s="3" t="n"/>
+      <c r="AZ11" s="9" t="n">
+        <v>86.35000000000045</v>
+      </c>
+      <c r="BA11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AZ11" s="10" t="n">
-        <v>79.15416666666707</v>
-      </c>
-      <c r="BA11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" s="10" t="n">
-        <v>79.15416666666707</v>
-      </c>
-      <c r="BC11" s="5" t="n">
-        <v>157</v>
-      </c>
-      <c r="BD11" s="5" t="n">
-        <v>157</v>
-      </c>
-      <c r="BE11" s="7" t="n">
-        <v>11</v>
-      </c>
+      <c r="BB11" s="9" t="n">
+        <v>86.35000000000045</v>
+      </c>
+      <c r="BC11" s="10" t="n"/>
+      <c r="BD11" s="10" t="n"/>
+      <c r="BE11" s="6" t="n"/>
       <c r="BF11" s="3" t="n"/>
       <c r="BG11" s="3" t="n"/>
       <c r="BH11" s="3" t="n"/>
